--- a/data/New Microsoft Excel Worksheet.xlsx
+++ b/data/New Microsoft Excel Worksheet.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E-M-W-E\Downloads\MyGithub\Profit-and-Loss-Analyzer\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7191595-4559-4C60-9A04-8599E49040AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +339,333 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="F8:L21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="8" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
+      <c r="K12">
+        <v>5</v>
+      </c>
+      <c r="L12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>6</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>6</v>
+      </c>
+      <c r="L13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>7</v>
+      </c>
+      <c r="H14">
+        <v>7</v>
+      </c>
+      <c r="I14">
+        <v>7</v>
+      </c>
+      <c r="J14">
+        <v>7</v>
+      </c>
+      <c r="K14">
+        <v>7</v>
+      </c>
+      <c r="L14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>8</v>
+      </c>
+      <c r="J15">
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <v>8</v>
+      </c>
+      <c r="L15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>9</v>
+      </c>
+      <c r="I16">
+        <v>9</v>
+      </c>
+      <c r="J16">
+        <v>9</v>
+      </c>
+      <c r="K16">
+        <v>9</v>
+      </c>
+      <c r="L16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>10</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>11</v>
+      </c>
+      <c r="H18">
+        <v>11</v>
+      </c>
+      <c r="I18">
+        <v>11</v>
+      </c>
+      <c r="J18">
+        <v>11</v>
+      </c>
+      <c r="K18">
+        <v>11</v>
+      </c>
+      <c r="L18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>12</v>
+      </c>
+      <c r="J19">
+        <v>12</v>
+      </c>
+      <c r="K19">
+        <v>12</v>
+      </c>
+      <c r="L19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>13</v>
+      </c>
+      <c r="I20">
+        <v>13</v>
+      </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
+      <c r="K20">
+        <v>13</v>
+      </c>
+      <c r="L20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="6:12" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>14</v>
+      </c>
+      <c r="G21">
+        <v>14</v>
+      </c>
+      <c r="H21">
+        <v>14</v>
+      </c>
+      <c r="I21">
+        <v>14</v>
+      </c>
+      <c r="J21">
+        <v>14</v>
+      </c>
+      <c r="K21">
+        <v>14</v>
+      </c>
+      <c r="L21">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/New Microsoft Excel Worksheet.xlsx
+++ b/data/New Microsoft Excel Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E-M-W-E\Downloads\MyGithub\Profit-and-Loss-Analyzer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7191595-4559-4C60-9A04-8599E49040AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6429A4-B288-46E1-BD51-98882FC43056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -340,10 +340,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="F8:L21"/>
+  <dimension ref="F8:I21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="8" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F8">
         <v>1</v>
       </c>
@@ -356,17 +356,8 @@
       <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F9">
         <v>2</v>
       </c>
@@ -379,17 +370,8 @@
       <c r="I9">
         <v>2</v>
       </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F10">
         <v>3</v>
       </c>
@@ -402,17 +384,8 @@
       <c r="I10">
         <v>3</v>
       </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-      <c r="K10">
-        <v>3</v>
-      </c>
-      <c r="L10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F11">
         <v>4</v>
       </c>
@@ -425,17 +398,8 @@
       <c r="I11">
         <v>4</v>
       </c>
-      <c r="J11">
-        <v>4</v>
-      </c>
-      <c r="K11">
-        <v>4</v>
-      </c>
-      <c r="L11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F12">
         <v>5</v>
       </c>
@@ -448,17 +412,8 @@
       <c r="I12">
         <v>5</v>
       </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
-      </c>
-      <c r="L12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F13">
         <v>6</v>
       </c>
@@ -471,17 +426,8 @@
       <c r="I13">
         <v>6</v>
       </c>
-      <c r="J13">
-        <v>6</v>
-      </c>
-      <c r="K13">
-        <v>6</v>
-      </c>
-      <c r="L13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F14">
         <v>7</v>
       </c>
@@ -494,17 +440,8 @@
       <c r="I14">
         <v>7</v>
       </c>
-      <c r="J14">
-        <v>7</v>
-      </c>
-      <c r="K14">
-        <v>7</v>
-      </c>
-      <c r="L14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F15">
         <v>8</v>
       </c>
@@ -517,17 +454,8 @@
       <c r="I15">
         <v>8</v>
       </c>
-      <c r="J15">
-        <v>8</v>
-      </c>
-      <c r="K15">
-        <v>8</v>
-      </c>
-      <c r="L15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F16">
         <v>9</v>
       </c>
@@ -540,17 +468,8 @@
       <c r="I16">
         <v>9</v>
       </c>
-      <c r="J16">
-        <v>9</v>
-      </c>
-      <c r="K16">
-        <v>9</v>
-      </c>
-      <c r="L16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F17">
         <v>10</v>
       </c>
@@ -563,17 +482,8 @@
       <c r="I17">
         <v>10</v>
       </c>
-      <c r="J17">
-        <v>10</v>
-      </c>
-      <c r="K17">
-        <v>10</v>
-      </c>
-      <c r="L17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F18">
         <v>11</v>
       </c>
@@ -586,17 +496,8 @@
       <c r="I18">
         <v>11</v>
       </c>
-      <c r="J18">
-        <v>11</v>
-      </c>
-      <c r="K18">
-        <v>11</v>
-      </c>
-      <c r="L18">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F19">
         <v>12</v>
       </c>
@@ -609,17 +510,8 @@
       <c r="I19">
         <v>12</v>
       </c>
-      <c r="J19">
-        <v>12</v>
-      </c>
-      <c r="K19">
-        <v>12</v>
-      </c>
-      <c r="L19">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F20">
         <v>13</v>
       </c>
@@ -632,17 +524,8 @@
       <c r="I20">
         <v>13</v>
       </c>
-      <c r="J20">
-        <v>13</v>
-      </c>
-      <c r="K20">
-        <v>13</v>
-      </c>
-      <c r="L20">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="6:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F21">
         <v>14</v>
       </c>
@@ -653,15 +536,6 @@
         <v>14</v>
       </c>
       <c r="I21">
-        <v>14</v>
-      </c>
-      <c r="J21">
-        <v>14</v>
-      </c>
-      <c r="K21">
-        <v>14</v>
-      </c>
-      <c r="L21">
         <v>14</v>
       </c>
     </row>
